--- a/excel/banking man.xlsx
+++ b/excel/banking man.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{521BC177-F22E-4590-83A6-F6AC048F87F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5459FB30-B7C6-4DFD-B210-AC480CCA29A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{47BF2AA7-7375-4884-91DE-46AD98CD43FB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>총 사업자수</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -39,11 +39,39 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>총 인구</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 총 사업자(넥타이 착용)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사전확률</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사후확률_P(산업/넥타이)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건부확률_P(넥타이/산업)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prior</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Likelihood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>총 사업자 수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>계산 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>계산 2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -51,10 +79,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="0.0000000"/>
+    <numFmt numFmtId="178" formatCode="0.000000"/>
+    <numFmt numFmtId="185" formatCode="0.0000%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,16 +125,31 @@
       <charset val="129"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -131,6 +177,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -143,7 +204,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -168,17 +229,41 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -209,8 +294,8 @@
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>412317</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>290397</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>144927</xdr:rowOff>
     </xdr:to>
@@ -237,6 +322,282 @@
         <a:xfrm>
           <a:off x="60960" y="53340"/>
           <a:ext cx="9655377" cy="1691787"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1021079</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>172344</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6ADD50B-6B81-8692-793F-3772238F3F05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5821679" y="3009900"/>
+          <a:ext cx="6149341" cy="1467744"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2346960</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>274513</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>129592</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DC0BBB1-56CC-09D4-94A7-F30C976ACEE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{BEBA8EAE-BF5A-486C-A8C5-ECC9F3942E4B}">
+              <a14:imgProps xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a14:imgLayer r:embed="rId4">
+                  <a14:imgEffect>
+                    <a14:brightnessContrast bright="-20000"/>
+                  </a14:imgEffect>
+                </a14:imgLayer>
+              </a14:imgProps>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7467600" y="6758940"/>
+          <a:ext cx="2232853" cy="594412"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1691769</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>861124</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4412FF9-DF1C-3B5C-DCB0-1C319026CAF6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7543800" y="4671060"/>
+          <a:ext cx="1493649" cy="739204"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1585049</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>906854</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C673E890-B34D-C63B-41F9-D9EC20B5A588}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9662160" y="4602480"/>
+          <a:ext cx="1028789" cy="853514"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1135380</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2087963</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>899221</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AEB1052-8255-3F1A-AC70-72CC1385FC06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5935980" y="4739640"/>
+          <a:ext cx="952583" cy="708721"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1112573</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>838261</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00E9D3BA-213F-EFC7-6A77-E66921BF3755}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4206240" y="4686300"/>
+          <a:ext cx="617273" cy="701101"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -545,59 +906,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BF71A41-DDD1-4B25-9A9A-016282001B42}">
-  <dimension ref="B10:G15"/>
+  <dimension ref="A10:G23"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.796875" style="1"/>
     <col min="2" max="2" width="14.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.796875" style="1"/>
-    <col min="6" max="6" width="10.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.796875" style="1"/>
+    <col min="4" max="4" width="18.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="33.3984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="19" t="s">
+        <v>10</v>
+      </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="2" t="s">
-        <v>3</v>
-      </c>
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="2"/>
       <c r="C11" s="5">
         <v>6246489</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <f>D12+D13</f>
         <v>986483.85</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="2">
         <v>66014</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <f>C12*0.9</f>
         <v>59412.6</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="10">
         <v>0.9</v>
       </c>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
@@ -605,15 +968,15 @@
         <f>C11-C12</f>
         <v>6180475</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <f>C13*0.15</f>
         <v>927071.25</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="10">
         <v>0.15</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="6">
         <f>C12/C11</f>
         <v>1.0568176778987365E-2</v>
@@ -623,7 +986,99 @@
         <v>6.0226632194738922E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="84.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="2:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="14">
+        <v>6246489</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="14">
+        <v>66014</v>
+      </c>
+      <c r="D18" s="13">
+        <f>C18/C17</f>
+        <v>1.0568176778987365E-2</v>
+      </c>
+      <c r="E18" s="13">
+        <f>E12</f>
+        <v>0.9</v>
+      </c>
+      <c r="F18" s="15">
+        <f>D18*E18</f>
+        <v>9.5113591010886275E-3</v>
+      </c>
+      <c r="G18" s="13">
+        <f>F18/F20</f>
+        <v>6.0226632194738922E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="14">
+        <f>C17-C18</f>
+        <v>6180475</v>
+      </c>
+      <c r="D19" s="13">
+        <f>C19/C17</f>
+        <v>0.98943182322101264</v>
+      </c>
+      <c r="E19" s="13">
+        <f>E13</f>
+        <v>0.15</v>
+      </c>
+      <c r="F19" s="15">
+        <f>D19*E19</f>
+        <v>0.14841477348315188</v>
+      </c>
+      <c r="G19" s="13">
+        <f>F19/F20</f>
+        <v>0.939773367805261</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F20" s="16">
+        <f>SUM(F18:F19)</f>
+        <v>0.15792613258424051</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B23" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
